--- a/artifacts/test_dashboard/report.xlsx
+++ b/artifacts/test_dashboard/report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdout Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecasts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Holdout Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Forecasts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -423,74 +423,12 @@
           <t>Game_ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Obs_Window</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>off_by_10_pct</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>off_by_20_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>probability_clients</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>probability_stakes</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SYS::Game A</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>14</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SYS::Game A</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>21</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9</v>
+          <t>SYS::Review</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -504,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +458,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>predicted_clients_week_4</t>
+          <t>predicted_clients</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -530,19 +468,34 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>predicted_stakes_week_4</t>
+          <t>predicted_stakes</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
           <t>confidence_stakes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>requires_review</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>review_reason</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>review_priority</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SYS::Game A</t>
+          <t>SYS::Review</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -551,16 +504,58 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E2" t="n">
         <v>100</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.8</v>
       </c>
-      <c r="E2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.7</v>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>low clients confidence</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SYS::Routine</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SYS</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
